--- a/public/templates/FasilitasInformasi.xlsx
+++ b/public/templates/FasilitasInformasi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E048253E-066B-4D11-90FB-82AD136680A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D92BC0-9173-490E-B763-51AA53B9FD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4DC7BE39-A07E-4B60-8BCD-E2E1B2E7F76D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4DC7BE39-A07E-4B60-8BCD-E2E1B2E7F76D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -261,6 +259,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -278,42 +312,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -653,143 +651,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2ACEFCF-9923-46E1-8DDC-5B321E2D39D3}">
   <dimension ref="B4:N9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="2" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="4"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="8"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="2">
-        <v>2021</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="2">
-        <v>2022</v>
-      </c>
-      <c r="N5" s="4"/>
+    <row r="5" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11">
+        <v>2024</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="11">
+        <v>2025</v>
+      </c>
+      <c r="N5" s="13"/>
     </row>
-    <row r="6" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="15"/>
     </row>
-    <row r="7" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="15"/>
     </row>
-    <row r="9" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="C4:J5"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
